--- a/artfynd/A 29704-2026 artfynd.xlsx
+++ b/artfynd/A 29704-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042872</v>
       </c>
       <c r="B2" t="n">
-        <v>106417</v>
+        <v>106418</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042873</v>
       </c>
       <c r="B3" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136042874</v>
       </c>
       <c r="B4" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29704-2026 artfynd.xlsx
+++ b/artfynd/A 29704-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042872</v>
       </c>
       <c r="B2" t="n">
-        <v>106418</v>
+        <v>106420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042873</v>
       </c>
       <c r="B3" t="n">
-        <v>99213</v>
+        <v>99214</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136042874</v>
       </c>
       <c r="B4" t="n">
-        <v>99213</v>
+        <v>99214</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29704-2026 artfynd.xlsx
+++ b/artfynd/A 29704-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042872</v>
       </c>
       <c r="B2" t="n">
-        <v>106420</v>
+        <v>106421</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042873</v>
       </c>
       <c r="B3" t="n">
-        <v>99214</v>
+        <v>99215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136042874</v>
       </c>
       <c r="B4" t="n">
-        <v>99214</v>
+        <v>99215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29704-2026 artfynd.xlsx
+++ b/artfynd/A 29704-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042872</v>
       </c>
       <c r="B2" t="n">
-        <v>106421</v>
+        <v>106422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042873</v>
       </c>
       <c r="B3" t="n">
-        <v>99215</v>
+        <v>99216</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136042874</v>
       </c>
       <c r="B4" t="n">
-        <v>99215</v>
+        <v>99216</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29704-2026 artfynd.xlsx
+++ b/artfynd/A 29704-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042872</v>
       </c>
       <c r="B2" t="n">
-        <v>106422</v>
+        <v>106428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042873</v>
       </c>
       <c r="B3" t="n">
-        <v>99216</v>
+        <v>99222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136042874</v>
       </c>
       <c r="B4" t="n">
-        <v>99216</v>
+        <v>99222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29704-2026 artfynd.xlsx
+++ b/artfynd/A 29704-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042872</v>
       </c>
       <c r="B2" t="n">
-        <v>106428</v>
+        <v>106429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042873</v>
       </c>
       <c r="B3" t="n">
-        <v>99222</v>
+        <v>99223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136042874</v>
       </c>
       <c r="B4" t="n">
-        <v>99222</v>
+        <v>99223</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29704-2026 artfynd.xlsx
+++ b/artfynd/A 29704-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042872</v>
       </c>
       <c r="B2" t="n">
-        <v>106429</v>
+        <v>106440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042873</v>
       </c>
       <c r="B3" t="n">
-        <v>99223</v>
+        <v>99234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136042874</v>
       </c>
       <c r="B4" t="n">
-        <v>99223</v>
+        <v>99234</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29704-2026 artfynd.xlsx
+++ b/artfynd/A 29704-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042872</v>
       </c>
       <c r="B2" t="n">
-        <v>106440</v>
+        <v>106453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042873</v>
       </c>
       <c r="B3" t="n">
-        <v>99234</v>
+        <v>99247</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136042874</v>
       </c>
       <c r="B4" t="n">
-        <v>99234</v>
+        <v>99247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29704-2026 artfynd.xlsx
+++ b/artfynd/A 29704-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042872</v>
       </c>
       <c r="B2" t="n">
-        <v>106453</v>
+        <v>106454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042873</v>
       </c>
       <c r="B3" t="n">
-        <v>99247</v>
+        <v>99248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136042874</v>
       </c>
       <c r="B4" t="n">
-        <v>99247</v>
+        <v>99248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29704-2026 artfynd.xlsx
+++ b/artfynd/A 29704-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042872</v>
       </c>
       <c r="B2" t="n">
-        <v>106454</v>
+        <v>106467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042873</v>
       </c>
       <c r="B3" t="n">
-        <v>99248</v>
+        <v>99261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136042874</v>
       </c>
       <c r="B4" t="n">
-        <v>99248</v>
+        <v>99261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29704-2026 artfynd.xlsx
+++ b/artfynd/A 29704-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042872</v>
       </c>
       <c r="B2" t="n">
-        <v>106467</v>
+        <v>106468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042873</v>
       </c>
       <c r="B3" t="n">
-        <v>99261</v>
+        <v>99262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136042874</v>
       </c>
       <c r="B4" t="n">
-        <v>99261</v>
+        <v>99262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
